--- a/src/data/ሳልሳይ.xlsx
+++ b/src/data/ሳልሳይ.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>id</t>
   </si>
@@ -34,34 +34,55 @@
     <t xml:space="preserve">የዩሐንስ ወንጌል አንድምታ</t>
   </si>
   <si>
-    <t xml:space="preserve">የማቴዎስ ወንጌል አንድምታ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">የሉቃስ ወንጌል አንድምታ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">የማርቆስ ወንጌል አንድምታ</t>
-  </si>
-  <si>
-    <t>ፍብመ/1105/18</t>
+    <t>ፍብመ/1103/18</t>
   </si>
   <si>
     <t>ሳልሳይ</t>
   </si>
   <si>
+    <t xml:space="preserve">ሐዊ ቶሉ</t>
+  </si>
+  <si>
+    <t>ፍብመ/1108/18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ምስክር አድማሱ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">በላይ በየነ</t>
+  </si>
+  <si>
+    <t>ፍብመ/1104/19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ባሮክ ፍቃዱ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ብርቱካን አማረ</t>
+  </si>
+  <si>
+    <t>ፍብመ/1106/21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ትዕግስት የትዋለ</t>
+  </si>
+  <si>
+    <t>ፍብመ/1102/22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ትዕግስት ደጄ</t>
+  </si>
+  <si>
+    <t>ፍብመ/1105/23</t>
+  </si>
+  <si>
     <t xml:space="preserve">አብርሃም ደሳለኝ</t>
   </si>
   <si>
-    <t>ፍብመ/1107/18</t>
+    <t>ፍብመ/1107/24</t>
   </si>
   <si>
     <t xml:space="preserve">ደሳለኝ ወልዴ</t>
-  </si>
-  <si>
-    <t>ፍብመ/1108/18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ዲ/ን ምስክር አድማሱ </t>
   </si>
   <si>
     <t>ፍብመ/1101/18</t>
@@ -153,10 +174,11 @@
     <xf fontId="2" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf fontId="2" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment wrapText="1"/>
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyProtection="0">
+    <xf fontId="2" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyProtection="0">
       <protection hidden="0" locked="1"/>
     </xf>
   </cellXfs>
@@ -597,118 +619,171 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="2" ht="14.25">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D2" s="4">
-        <v>71.5</v>
+        <v>29</v>
       </c>
       <c r="E2" s="4">
-        <v>90</v>
-      </c>
-      <c r="F2" s="4">
-        <v>90</v>
-      </c>
-      <c r="G2" s="4">
-        <v>90</v>
-      </c>
-      <c r="H2" s="4">
-        <v>90</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" ht="14.25">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="D3" s="4">
-        <v>89.5</v>
+        <v>33.5</v>
       </c>
       <c r="E3" s="4">
-        <v>70</v>
-      </c>
-      <c r="F3" s="4">
-        <v>70</v>
-      </c>
-      <c r="G3" s="4">
-        <v>70</v>
-      </c>
-      <c r="H3" s="4">
-        <v>70</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="4" ht="14.25">
-      <c r="A4" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D4" s="4">
-        <v>89</v>
+        <v>34.5</v>
       </c>
       <c r="E4" s="4">
-        <v>28</v>
-      </c>
-      <c r="F4" s="4">
-        <v>28</v>
-      </c>
-      <c r="G4" s="4">
-        <v>28</v>
-      </c>
-      <c r="H4" s="4">
-        <v>28</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" ht="14.25">
       <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="4">
+        <v>20</v>
+      </c>
+      <c r="E5" s="4">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" ht="12.75">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="4">
+        <v>34</v>
+      </c>
+      <c r="E6" s="4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" ht="12.75">
+      <c r="A7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="D7" s="4">
+        <v>18</v>
+      </c>
+      <c r="E7" s="4">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" ht="12.75">
+      <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="4">
-        <v>93.5</v>
-      </c>
-      <c r="E5" s="4">
-        <v>100</v>
-      </c>
-      <c r="F5" s="4">
-        <v>100</v>
-      </c>
-      <c r="G5" s="4">
-        <v>100</v>
-      </c>
-      <c r="H5" s="4">
-        <v>100</v>
+      <c r="B8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="4">
+        <v>36</v>
+      </c>
+      <c r="E8" s="4">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" ht="12.75">
+      <c r="A9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="4">
+        <v>22</v>
+      </c>
+      <c r="E9" s="4">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="10" ht="12.75">
+      <c r="A10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="4">
+        <v>32.5</v>
+      </c>
+      <c r="E10" s="4">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" ht="12.75">
+      <c r="A11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="4">
+        <v>36.5</v>
+      </c>
+      <c r="E11" s="4">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/src/data/ሳልሳይ.xlsx
+++ b/src/data/ሳልሳይ.xlsx
@@ -40,55 +40,55 @@
     <t>ሳልሳይ</t>
   </si>
   <si>
-    <t xml:space="preserve">ሐዊ ቶሉ</t>
+    <t xml:space="preserve">ሐዊ ቶሉ ቂጣታ</t>
   </si>
   <si>
     <t>ፍብመ/1108/18</t>
   </si>
   <si>
-    <t xml:space="preserve">ምስክር አድማሱ</t>
+    <t xml:space="preserve">ምስክር አድማሱ አለሙ</t>
   </si>
   <si>
     <t xml:space="preserve">በላይ በየነ</t>
   </si>
   <si>
-    <t>ፍብመ/1104/19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ባሮክ ፍቃዱ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ብርቱካን አማረ</t>
-  </si>
-  <si>
-    <t>ፍብመ/1106/21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ትዕግስት የትዋለ</t>
-  </si>
-  <si>
-    <t>ፍብመ/1102/22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ትዕግስት ደጄ</t>
-  </si>
-  <si>
-    <t>ፍብመ/1105/23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">አብርሃም ደሳለኝ</t>
-  </si>
-  <si>
-    <t>ፍብመ/1107/24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ደሳለኝ ወልዴ</t>
+    <t>ፍብመ/1104/18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ባሮክ ፍቃዱ ጀማል</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ብርቱካን አማረ </t>
+  </si>
+  <si>
+    <t>ፍብመ/1106/18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ትዕግስት የትዋለ ቢረሳው</t>
+  </si>
+  <si>
+    <t>ፍብመ/1102/18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ትዕግስት ደጄ አበራ</t>
+  </si>
+  <si>
+    <t>ፍብመ/1105/18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">አብርሃም ደሳለኝ ሸለማ</t>
+  </si>
+  <si>
+    <t>ፍብመ/1107/18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ደሳለኝ ወልዴ ሽፈራው</t>
   </si>
   <si>
     <t>ፍብመ/1101/18</t>
   </si>
   <si>
-    <t xml:space="preserve">ዳቢ ኃይሌ</t>
+    <t xml:space="preserve">ዳቢ ኃይሌ አለኡ</t>
   </si>
 </sst>
 </file>
@@ -686,7 +686,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" ht="12.75">
+    <row r="6" ht="14.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
         <v>6</v>
@@ -701,7 +701,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" ht="12.75">
+    <row r="7" ht="14.25">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
@@ -718,7 +718,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" ht="12.75">
+    <row r="8" ht="14.25">
       <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
@@ -735,7 +735,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" ht="12.75">
+    <row r="9" ht="14.25">
       <c r="A9" s="2" t="s">
         <v>18</v>
       </c>
@@ -752,7 +752,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="10" ht="12.75">
+    <row r="10" ht="14.25">
       <c r="A10" s="2" t="s">
         <v>20</v>
       </c>
@@ -769,7 +769,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" ht="12.75">
+    <row r="11" ht="14.25">
       <c r="A11" s="2" t="s">
         <v>22</v>
       </c>

--- a/src/data/ሳልሳይ.xlsx
+++ b/src/data/ሳልሳይ.xlsx
@@ -88,7 +88,7 @@
     <t>ፍብመ/1101/18</t>
   </si>
   <si>
-    <t xml:space="preserve">ዳቢ ኃይሌ አለኡ</t>
+    <t xml:space="preserve">ዳቢ ኃይሌ አለሙ</t>
   </si>
 </sst>
 </file>
@@ -163,7 +163,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
       <protection hidden="0" locked="1"/>
     </xf>
@@ -176,6 +176,9 @@
     </xf>
     <xf fontId="2" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment wrapText="1"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyProtection="0">
       <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="2" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyProtection="0">
@@ -631,10 +634,10 @@
         <v>7</v>
       </c>
       <c r="D2" s="4">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="E2" s="4">
-        <v>51</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" ht="14.25">
@@ -648,10 +651,10 @@
         <v>9</v>
       </c>
       <c r="D3" s="4">
-        <v>33.5</v>
+        <v>89</v>
       </c>
       <c r="E3" s="4">
-        <v>55.5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" ht="14.25">
@@ -663,10 +666,10 @@
         <v>10</v>
       </c>
       <c r="D4" s="4">
-        <v>34.5</v>
+        <v>79.5</v>
       </c>
       <c r="E4" s="4">
-        <v>45</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" ht="14.25">
@@ -680,10 +683,10 @@
         <v>12</v>
       </c>
       <c r="D5" s="4">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="E5" s="4">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" ht="14.25">
@@ -691,14 +694,14 @@
       <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D6" s="4">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="E6" s="4">
-        <v>51</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" ht="14.25">
@@ -708,14 +711,14 @@
       <c r="B7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="4">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="E7" s="4">
-        <v>57</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" ht="14.25">
@@ -725,14 +728,14 @@
       <c r="B8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D8" s="4">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="E8" s="4">
-        <v>54</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" ht="14.25">
@@ -742,14 +745,14 @@
       <c r="B9" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D9" s="4">
-        <v>22</v>
+        <v>71.5</v>
       </c>
       <c r="E9" s="4">
-        <v>49.5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" ht="14.25">
@@ -759,14 +762,14 @@
       <c r="B10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D10" s="4">
-        <v>32.5</v>
+        <v>89.5</v>
       </c>
       <c r="E10" s="4">
-        <v>57</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" ht="14.25">
@@ -776,19 +779,19 @@
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D11" s="4">
-        <v>36.5</v>
+        <v>93.5</v>
       </c>
       <c r="E11" s="4">
-        <v>57</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="C2:E5" columnSort="0">
-    <sortCondition sortBy="value" descending="0" ref="C1:C5"/>
+  <sortState ref="A2:E11" columnSort="0">
+    <sortCondition sortBy="value" descending="0" ref="C2:C11"/>
   </sortState>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
